--- a/artfynd/A 57727-2023 artfynd.xlsx
+++ b/artfynd/A 57727-2023 artfynd.xlsx
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117894219</v>
+        <v>117894195</v>
       </c>
       <c r="B10" t="n">
         <v>57287</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>450218</v>
+        <v>450161</v>
       </c>
       <c r="R10" t="n">
-        <v>7088983</v>
+        <v>7088668</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117894195</v>
+        <v>117894181</v>
       </c>
       <c r="B11" t="n">
         <v>57287</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450161</v>
+        <v>450159</v>
       </c>
       <c r="R11" t="n">
-        <v>7088668</v>
+        <v>7088815</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117894181</v>
+        <v>117894219</v>
       </c>
       <c r="B12" t="n">
         <v>57287</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450159</v>
+        <v>450218</v>
       </c>
       <c r="R12" t="n">
-        <v>7088815</v>
+        <v>7088983</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117894178</v>
+        <v>117894226</v>
       </c>
       <c r="B18" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2403,21 +2403,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>450115</v>
+        <v>449958</v>
       </c>
       <c r="R18" t="n">
-        <v>7088874</v>
+        <v>7088997</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2463,11 +2463,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,7 +2489,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117894199</v>
+        <v>117894178</v>
       </c>
       <c r="B19" t="n">
         <v>57287</v>
@@ -2534,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>450248</v>
+        <v>450115</v>
       </c>
       <c r="R19" t="n">
-        <v>7088702</v>
+        <v>7088874</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,7 +2569,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,10 +2596,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117894226</v>
+        <v>117894199</v>
       </c>
       <c r="B20" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2617,21 +2612,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2641,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>449958</v>
+        <v>450248</v>
       </c>
       <c r="R20" t="n">
-        <v>7088997</v>
+        <v>7088702</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2677,6 +2672,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2703,10 +2703,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117894162</v>
+        <v>117894222</v>
       </c>
       <c r="B21" t="n">
-        <v>90499</v>
+        <v>57287</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2719,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>450228</v>
+        <v>450034</v>
       </c>
       <c r="R21" t="n">
-        <v>7088763</v>
+        <v>7088998</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2779,6 +2779,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,7 +2810,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117894222</v>
+        <v>117894172</v>
       </c>
       <c r="B22" t="n">
         <v>57287</v>
@@ -2845,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>450034</v>
+        <v>449956</v>
       </c>
       <c r="R22" t="n">
-        <v>7088998</v>
+        <v>7089019</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2912,10 +2917,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117894172</v>
+        <v>117894162</v>
       </c>
       <c r="B23" t="n">
-        <v>57287</v>
+        <v>90499</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2928,21 +2933,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2952,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>449956</v>
+        <v>450228</v>
       </c>
       <c r="R23" t="n">
-        <v>7089019</v>
+        <v>7088763</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2988,11 +2993,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3656,10 +3656,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117894238</v>
+        <v>117894173</v>
       </c>
       <c r="B30" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3672,21 +3672,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>449964</v>
+        <v>449951</v>
       </c>
       <c r="R30" t="n">
-        <v>7089143</v>
+        <v>7089007</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3732,6 +3732,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3758,7 +3763,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117894173</v>
+        <v>117894201</v>
       </c>
       <c r="B31" t="n">
         <v>57287</v>
@@ -3798,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>449951</v>
+        <v>450252</v>
       </c>
       <c r="R31" t="n">
-        <v>7089007</v>
+        <v>7088672</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,7 +3843,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3865,10 +3870,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117894201</v>
+        <v>117894238</v>
       </c>
       <c r="B32" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3881,21 +3886,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3905,10 +3910,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>450252</v>
+        <v>449964</v>
       </c>
       <c r="R32" t="n">
-        <v>7088672</v>
+        <v>7089143</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3941,11 +3946,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5348,7 +5348,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117894198</v>
+        <v>117894174</v>
       </c>
       <c r="B46" t="n">
         <v>57287</v>
@@ -5388,10 +5388,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>450236</v>
+        <v>449965</v>
       </c>
       <c r="R46" t="n">
-        <v>7088721</v>
+        <v>7088991</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5455,10 +5455,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117894232</v>
+        <v>117894194</v>
       </c>
       <c r="B47" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5471,21 +5471,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5495,10 +5495,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>450219</v>
+        <v>450163</v>
       </c>
       <c r="R47" t="n">
-        <v>7088785</v>
+        <v>7088675</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5531,6 +5531,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5557,10 +5562,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117894228</v>
+        <v>117894198</v>
       </c>
       <c r="B48" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5573,21 +5578,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5597,10 +5602,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>450144</v>
+        <v>450236</v>
       </c>
       <c r="R48" t="n">
-        <v>7088852</v>
+        <v>7088721</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5633,6 +5638,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5659,10 +5669,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117894174</v>
+        <v>117894232</v>
       </c>
       <c r="B49" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5675,21 +5685,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5699,10 +5709,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>449965</v>
+        <v>450219</v>
       </c>
       <c r="R49" t="n">
-        <v>7088991</v>
+        <v>7088785</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5735,11 +5745,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5766,10 +5771,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117894194</v>
+        <v>117894228</v>
       </c>
       <c r="B50" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5782,21 +5787,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5806,10 +5811,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>450163</v>
+        <v>450144</v>
       </c>
       <c r="R50" t="n">
-        <v>7088675</v>
+        <v>7088852</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5842,11 +5847,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 57727-2023 artfynd.xlsx
+++ b/artfynd/A 57727-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117894164</v>
+        <v>117894170</v>
       </c>
       <c r="B2" t="n">
         <v>57287</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>449836</v>
+        <v>449884</v>
       </c>
       <c r="R2" t="n">
-        <v>7089280</v>
+        <v>7089103</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117894170</v>
+        <v>117894167</v>
       </c>
       <c r="B4" t="n">
         <v>57287</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>449884</v>
+        <v>449784</v>
       </c>
       <c r="R4" t="n">
-        <v>7089103</v>
+        <v>7089210</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117894165</v>
+        <v>117894164</v>
       </c>
       <c r="B5" t="n">
         <v>57287</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449804</v>
+        <v>449836</v>
       </c>
       <c r="R5" t="n">
-        <v>7089213</v>
+        <v>7089280</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117894167</v>
+        <v>117894165</v>
       </c>
       <c r="B6" t="n">
         <v>57287</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449784</v>
+        <v>449804</v>
       </c>
       <c r="R6" t="n">
-        <v>7089210</v>
+        <v>7089213</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117894191</v>
+        <v>117894163</v>
       </c>
       <c r="B8" t="n">
-        <v>57287</v>
+        <v>90499</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>450212</v>
+        <v>450323</v>
       </c>
       <c r="R8" t="n">
-        <v>7088718</v>
+        <v>7088910</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,11 +1393,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117894183</v>
+        <v>117894174</v>
       </c>
       <c r="B9" t="n">
         <v>57287</v>
@@ -1464,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>450106</v>
+        <v>449965</v>
       </c>
       <c r="R9" t="n">
-        <v>7088745</v>
+        <v>7088991</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117894195</v>
+        <v>117894182</v>
       </c>
       <c r="B10" t="n">
         <v>57287</v>
@@ -1571,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>450161</v>
+        <v>450065</v>
       </c>
       <c r="R10" t="n">
-        <v>7088668</v>
+        <v>7088758</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1606,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117894181</v>
+        <v>117894233</v>
       </c>
       <c r="B11" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1654,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1678,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450159</v>
+        <v>450244</v>
       </c>
       <c r="R11" t="n">
-        <v>7088815</v>
+        <v>7088764</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1714,11 +1709,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117894219</v>
+        <v>117894225</v>
       </c>
       <c r="B12" t="n">
         <v>57287</v>
@@ -1785,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>450218</v>
+        <v>449970</v>
       </c>
       <c r="R12" t="n">
-        <v>7088983</v>
+        <v>7089256</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117894218</v>
+        <v>117894201</v>
       </c>
       <c r="B13" t="n">
         <v>57287</v>
@@ -1892,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450300</v>
+        <v>450252</v>
       </c>
       <c r="R13" t="n">
-        <v>7088949</v>
+        <v>7088672</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117894225</v>
+        <v>117894224</v>
       </c>
       <c r="B14" t="n">
         <v>57287</v>
@@ -1999,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>449970</v>
+        <v>450022</v>
       </c>
       <c r="R14" t="n">
-        <v>7089256</v>
+        <v>7089009</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2066,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117894177</v>
+        <v>117894229</v>
       </c>
       <c r="B15" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2082,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2106,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>450121</v>
+        <v>450175</v>
       </c>
       <c r="R15" t="n">
-        <v>7088894</v>
+        <v>7088816</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2142,11 +2132,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117894197</v>
+        <v>117894227</v>
       </c>
       <c r="B16" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2189,21 +2174,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2213,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>450230</v>
+        <v>450123</v>
       </c>
       <c r="R16" t="n">
-        <v>7088707</v>
+        <v>7088854</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2249,11 +2234,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,7 +2260,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117894176</v>
+        <v>117894191</v>
       </c>
       <c r="B17" t="n">
         <v>57287</v>
@@ -2320,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>450138</v>
+        <v>450212</v>
       </c>
       <c r="R17" t="n">
-        <v>7088892</v>
+        <v>7088718</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2340,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,7 +2367,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117894226</v>
+        <v>117894228</v>
       </c>
       <c r="B18" t="n">
         <v>90517</v>
@@ -2427,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>449958</v>
+        <v>450144</v>
       </c>
       <c r="R18" t="n">
-        <v>7088997</v>
+        <v>7088852</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2489,7 +2469,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117894178</v>
+        <v>117894177</v>
       </c>
       <c r="B19" t="n">
         <v>57287</v>
@@ -2529,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>450115</v>
+        <v>450121</v>
       </c>
       <c r="R19" t="n">
-        <v>7088874</v>
+        <v>7088894</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2569,7 +2549,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2596,7 +2576,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117894199</v>
+        <v>117894197</v>
       </c>
       <c r="B20" t="n">
         <v>57287</v>
@@ -2636,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>450248</v>
+        <v>450230</v>
       </c>
       <c r="R20" t="n">
-        <v>7088702</v>
+        <v>7088707</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2703,7 +2683,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117894222</v>
+        <v>117894173</v>
       </c>
       <c r="B21" t="n">
         <v>57287</v>
@@ -2743,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>450034</v>
+        <v>449951</v>
       </c>
       <c r="R21" t="n">
-        <v>7088998</v>
+        <v>7089007</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,7 +2763,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2917,10 +2897,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117894162</v>
+        <v>117894218</v>
       </c>
       <c r="B23" t="n">
-        <v>90499</v>
+        <v>57287</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2933,21 +2913,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,10 +2937,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>450228</v>
+        <v>450300</v>
       </c>
       <c r="R23" t="n">
-        <v>7088763</v>
+        <v>7088949</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2993,6 +2973,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,7 +3004,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117894175</v>
+        <v>117894181</v>
       </c>
       <c r="B24" t="n">
         <v>57287</v>
@@ -3059,10 +3044,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>450026</v>
+        <v>450159</v>
       </c>
       <c r="R24" t="n">
-        <v>7088869</v>
+        <v>7088815</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3126,7 +3111,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117894224</v>
+        <v>117894193</v>
       </c>
       <c r="B25" t="n">
         <v>57287</v>
@@ -3166,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>450022</v>
+        <v>450165</v>
       </c>
       <c r="R25" t="n">
-        <v>7089009</v>
+        <v>7088687</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3233,10 +3218,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117894200</v>
+        <v>117894226</v>
       </c>
       <c r="B26" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3249,21 +3234,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3273,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>450233</v>
+        <v>449958</v>
       </c>
       <c r="R26" t="n">
-        <v>7088707</v>
+        <v>7088997</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3309,11 +3294,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3340,7 +3320,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117894190</v>
+        <v>117894219</v>
       </c>
       <c r="B27" t="n">
         <v>57287</v>
@@ -3380,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>450270</v>
+        <v>450218</v>
       </c>
       <c r="R27" t="n">
-        <v>7088751</v>
+        <v>7088983</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3400,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3447,10 +3427,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117894234</v>
+        <v>117894179</v>
       </c>
       <c r="B28" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3463,21 +3443,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3487,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>450212</v>
+        <v>450114</v>
       </c>
       <c r="R28" t="n">
-        <v>7088722</v>
+        <v>7088861</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3523,6 +3503,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3549,7 +3534,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117894182</v>
+        <v>117894185</v>
       </c>
       <c r="B29" t="n">
         <v>57287</v>
@@ -3589,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>450065</v>
+        <v>450127</v>
       </c>
       <c r="R29" t="n">
-        <v>7088758</v>
+        <v>7088766</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3629,7 +3614,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3656,7 +3641,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117894173</v>
+        <v>117894199</v>
       </c>
       <c r="B30" t="n">
         <v>57287</v>
@@ -3696,10 +3681,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>449951</v>
+        <v>450248</v>
       </c>
       <c r="R30" t="n">
-        <v>7089007</v>
+        <v>7088702</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3736,7 +3721,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3763,10 +3748,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117894201</v>
+        <v>117894238</v>
       </c>
       <c r="B31" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3779,21 +3764,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3803,10 +3788,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>450252</v>
+        <v>449964</v>
       </c>
       <c r="R31" t="n">
-        <v>7088672</v>
+        <v>7089143</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3839,11 +3824,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3870,10 +3850,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117894238</v>
+        <v>117894200</v>
       </c>
       <c r="B32" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3886,21 +3866,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3910,10 +3890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449964</v>
+        <v>450233</v>
       </c>
       <c r="R32" t="n">
-        <v>7089143</v>
+        <v>7088707</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3946,6 +3926,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3972,10 +3957,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117894227</v>
+        <v>117894222</v>
       </c>
       <c r="B33" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3988,21 +3973,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4012,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>450123</v>
+        <v>450034</v>
       </c>
       <c r="R33" t="n">
-        <v>7088854</v>
+        <v>7088998</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4048,6 +4033,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4074,7 +4064,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117894186</v>
+        <v>117894178</v>
       </c>
       <c r="B34" t="n">
         <v>57287</v>
@@ -4114,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>450114</v>
+        <v>450115</v>
       </c>
       <c r="R34" t="n">
-        <v>7088711</v>
+        <v>7088874</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4154,7 +4144,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4181,7 +4171,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117894179</v>
+        <v>117894180</v>
       </c>
       <c r="B35" t="n">
         <v>57287</v>
@@ -4221,10 +4211,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>450114</v>
+        <v>450149</v>
       </c>
       <c r="R35" t="n">
-        <v>7088861</v>
+        <v>7088855</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4261,7 +4251,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4288,10 +4278,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117894188</v>
+        <v>117894162</v>
       </c>
       <c r="B36" t="n">
-        <v>57287</v>
+        <v>90499</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4304,21 +4294,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4328,10 +4318,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>450177</v>
+        <v>450228</v>
       </c>
       <c r="R36" t="n">
-        <v>7088765</v>
+        <v>7088763</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4364,11 +4354,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4395,7 +4380,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117894196</v>
+        <v>117894183</v>
       </c>
       <c r="B37" t="n">
         <v>57287</v>
@@ -4435,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>450201</v>
+        <v>450106</v>
       </c>
       <c r="R37" t="n">
-        <v>7088663</v>
+        <v>7088745</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4502,7 +4487,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117894185</v>
+        <v>117894186</v>
       </c>
       <c r="B38" t="n">
         <v>57287</v>
@@ -4542,10 +4527,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>450127</v>
+        <v>450114</v>
       </c>
       <c r="R38" t="n">
-        <v>7088766</v>
+        <v>7088711</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4582,7 +4567,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4609,10 +4594,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117894163</v>
+        <v>117894175</v>
       </c>
       <c r="B39" t="n">
-        <v>90499</v>
+        <v>57287</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4625,21 +4610,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4649,10 +4634,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>450323</v>
+        <v>450026</v>
       </c>
       <c r="R39" t="n">
-        <v>7088910</v>
+        <v>7088869</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4685,6 +4670,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4711,10 +4701,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117894171</v>
+        <v>117894230</v>
       </c>
       <c r="B40" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4727,21 +4717,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4751,10 +4741,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>449982</v>
+        <v>450114</v>
       </c>
       <c r="R40" t="n">
-        <v>7089048</v>
+        <v>7088756</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4787,11 +4777,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4818,10 +4803,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117894180</v>
+        <v>117894234</v>
       </c>
       <c r="B41" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4834,21 +4819,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4858,10 +4843,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>450149</v>
+        <v>450212</v>
       </c>
       <c r="R41" t="n">
-        <v>7088855</v>
+        <v>7088722</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4894,11 +4879,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4925,10 +4905,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117894230</v>
+        <v>117894176</v>
       </c>
       <c r="B42" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4941,21 +4921,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4965,10 +4945,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>450114</v>
+        <v>450138</v>
       </c>
       <c r="R42" t="n">
-        <v>7088756</v>
+        <v>7088892</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5001,6 +4981,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5027,7 +5012,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117894193</v>
+        <v>117894195</v>
       </c>
       <c r="B43" t="n">
         <v>57287</v>
@@ -5067,10 +5052,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>450165</v>
+        <v>450161</v>
       </c>
       <c r="R43" t="n">
-        <v>7088687</v>
+        <v>7088668</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5107,7 +5092,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5134,7 +5119,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117894221</v>
+        <v>117894220</v>
       </c>
       <c r="B44" t="n">
         <v>57287</v>
@@ -5174,10 +5159,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>450095</v>
+        <v>450212</v>
       </c>
       <c r="R44" t="n">
-        <v>7088995</v>
+        <v>7088954</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5214,7 +5199,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5348,7 +5333,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117894174</v>
+        <v>117894198</v>
       </c>
       <c r="B46" t="n">
         <v>57287</v>
@@ -5388,10 +5373,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>449965</v>
+        <v>450236</v>
       </c>
       <c r="R46" t="n">
-        <v>7088991</v>
+        <v>7088721</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5455,7 +5440,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117894194</v>
+        <v>117894190</v>
       </c>
       <c r="B47" t="n">
         <v>57287</v>
@@ -5495,10 +5480,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>450163</v>
+        <v>450270</v>
       </c>
       <c r="R47" t="n">
-        <v>7088675</v>
+        <v>7088751</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5535,7 +5520,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5562,7 +5547,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117894198</v>
+        <v>117894194</v>
       </c>
       <c r="B48" t="n">
         <v>57287</v>
@@ -5602,10 +5587,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>450236</v>
+        <v>450163</v>
       </c>
       <c r="R48" t="n">
-        <v>7088721</v>
+        <v>7088675</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5642,7 +5627,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5669,10 +5654,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117894232</v>
+        <v>117894187</v>
       </c>
       <c r="B49" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5685,21 +5670,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5709,10 +5694,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>450219</v>
+        <v>450140</v>
       </c>
       <c r="R49" t="n">
-        <v>7088785</v>
+        <v>7088706</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5745,6 +5730,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5771,10 +5761,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117894228</v>
+        <v>117894171</v>
       </c>
       <c r="B50" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5787,21 +5777,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5811,10 +5801,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>450144</v>
+        <v>449982</v>
       </c>
       <c r="R50" t="n">
-        <v>7088852</v>
+        <v>7089048</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5847,6 +5837,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5873,10 +5868,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117894229</v>
+        <v>117894188</v>
       </c>
       <c r="B51" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5889,21 +5884,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5913,10 +5908,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>450175</v>
+        <v>450177</v>
       </c>
       <c r="R51" t="n">
-        <v>7088816</v>
+        <v>7088765</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5949,6 +5944,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5975,10 +5975,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117894220</v>
+        <v>117894232</v>
       </c>
       <c r="B52" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5991,21 +5991,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>450212</v>
+        <v>450219</v>
       </c>
       <c r="R52" t="n">
-        <v>7088954</v>
+        <v>7088785</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6051,11 +6051,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6082,10 +6077,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117894233</v>
+        <v>117894221</v>
       </c>
       <c r="B53" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6098,21 +6093,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6122,10 +6117,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>450244</v>
+        <v>450095</v>
       </c>
       <c r="R53" t="n">
-        <v>7088764</v>
+        <v>7088995</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6158,6 +6153,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6184,7 +6184,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117894187</v>
+        <v>117894196</v>
       </c>
       <c r="B54" t="n">
         <v>57287</v>
@@ -6224,10 +6224,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>450140</v>
+        <v>450201</v>
       </c>
       <c r="R54" t="n">
-        <v>7088706</v>
+        <v>7088663</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6291,7 +6291,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117894216</v>
+        <v>117894210</v>
       </c>
       <c r="B55" t="n">
         <v>57287</v>
@@ -6331,10 +6331,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>450452</v>
+        <v>450351</v>
       </c>
       <c r="R55" t="n">
-        <v>7088521</v>
+        <v>7088483</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6505,10 +6505,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117894236</v>
+        <v>117894204</v>
       </c>
       <c r="B57" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6521,21 +6521,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6545,10 +6545,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>450337</v>
+        <v>450385</v>
       </c>
       <c r="R57" t="n">
-        <v>7088500</v>
+        <v>7088570</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6581,6 +6581,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6607,10 +6612,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117894237</v>
+        <v>117894205</v>
       </c>
       <c r="B58" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6623,21 +6628,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6647,10 +6652,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>450435</v>
+        <v>450390</v>
       </c>
       <c r="R58" t="n">
-        <v>7088519</v>
+        <v>7088591</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6683,6 +6688,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6709,7 +6719,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117894235</v>
+        <v>117894237</v>
       </c>
       <c r="B59" t="n">
         <v>90517</v>
@@ -6749,10 +6759,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>450329</v>
+        <v>450435</v>
       </c>
       <c r="R59" t="n">
-        <v>7088601</v>
+        <v>7088519</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6811,7 +6821,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117894208</v>
+        <v>117894206</v>
       </c>
       <c r="B60" t="n">
         <v>57287</v>
@@ -6851,10 +6861,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>450348</v>
+        <v>450397</v>
       </c>
       <c r="R60" t="n">
-        <v>7088372</v>
+        <v>7088603</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6918,7 +6928,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117894210</v>
+        <v>117894208</v>
       </c>
       <c r="B61" t="n">
         <v>57287</v>
@@ -6958,10 +6968,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>450351</v>
+        <v>450348</v>
       </c>
       <c r="R61" t="n">
-        <v>7088483</v>
+        <v>7088372</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6998,7 +7008,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7025,7 +7035,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117894206</v>
+        <v>117894214</v>
       </c>
       <c r="B62" t="n">
         <v>57287</v>
@@ -7065,10 +7075,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>450397</v>
+        <v>450390</v>
       </c>
       <c r="R62" t="n">
-        <v>7088603</v>
+        <v>7088489</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7105,7 +7115,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7132,7 +7142,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117894204</v>
+        <v>117894209</v>
       </c>
       <c r="B63" t="n">
         <v>57287</v>
@@ -7172,10 +7182,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>450385</v>
+        <v>450295</v>
       </c>
       <c r="R63" t="n">
-        <v>7088570</v>
+        <v>7088392</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7239,7 +7249,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117894209</v>
+        <v>117894213</v>
       </c>
       <c r="B64" t="n">
         <v>57287</v>
@@ -7279,10 +7289,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>450295</v>
+        <v>450378</v>
       </c>
       <c r="R64" t="n">
-        <v>7088392</v>
+        <v>7088494</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7319,7 +7329,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7346,10 +7356,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117894207</v>
+        <v>117894236</v>
       </c>
       <c r="B65" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7362,21 +7372,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7386,10 +7396,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>450284</v>
+        <v>450337</v>
       </c>
       <c r="R65" t="n">
-        <v>7088356</v>
+        <v>7088500</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7422,11 +7432,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7453,10 +7458,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117894214</v>
+        <v>117894235</v>
       </c>
       <c r="B66" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7469,21 +7474,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7493,10 +7498,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>450390</v>
+        <v>450329</v>
       </c>
       <c r="R66" t="n">
-        <v>7088489</v>
+        <v>7088601</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7529,11 +7534,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7667,7 +7667,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117894205</v>
+        <v>117894207</v>
       </c>
       <c r="B68" t="n">
         <v>57287</v>
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>450390</v>
+        <v>450284</v>
       </c>
       <c r="R68" t="n">
-        <v>7088591</v>
+        <v>7088356</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7747,7 +7747,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7774,7 +7774,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117894213</v>
+        <v>117894216</v>
       </c>
       <c r="B69" t="n">
         <v>57287</v>
@@ -7814,10 +7814,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>450378</v>
+        <v>450452</v>
       </c>
       <c r="R69" t="n">
-        <v>7088494</v>
+        <v>7088521</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 57727-2023 artfynd.xlsx
+++ b/artfynd/A 57727-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117894170</v>
+        <v>117894165</v>
       </c>
       <c r="B2" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>449884</v>
+        <v>449804</v>
       </c>
       <c r="R2" t="n">
-        <v>7089103</v>
+        <v>7089213</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117894166</v>
+        <v>117894164</v>
       </c>
       <c r="B3" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>449786</v>
+        <v>449836</v>
       </c>
       <c r="R3" t="n">
-        <v>7089202</v>
+        <v>7089280</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +892,7 @@
         <v>117894167</v>
       </c>
       <c r="B4" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117894164</v>
+        <v>117894170</v>
       </c>
       <c r="B5" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449836</v>
+        <v>449884</v>
       </c>
       <c r="R5" t="n">
-        <v>7089280</v>
+        <v>7089103</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117894165</v>
+        <v>117894166</v>
       </c>
       <c r="B6" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449804</v>
+        <v>449786</v>
       </c>
       <c r="R6" t="n">
-        <v>7089213</v>
+        <v>7089202</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,7 +1213,7 @@
         <v>117894169</v>
       </c>
       <c r="B7" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117894163</v>
+        <v>117894238</v>
       </c>
       <c r="B8" t="n">
-        <v>90499</v>
+        <v>90519</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>450323</v>
+        <v>449964</v>
       </c>
       <c r="R8" t="n">
-        <v>7088910</v>
+        <v>7089143</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117894174</v>
+        <v>117894175</v>
       </c>
       <c r="B9" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449965</v>
+        <v>450026</v>
       </c>
       <c r="R9" t="n">
-        <v>7088991</v>
+        <v>7088869</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117894182</v>
+        <v>117894218</v>
       </c>
       <c r="B10" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>450065</v>
+        <v>450300</v>
       </c>
       <c r="R10" t="n">
-        <v>7088758</v>
+        <v>7088949</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117894233</v>
+        <v>117894190</v>
       </c>
       <c r="B11" t="n">
-        <v>90517</v>
+        <v>57288</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450244</v>
+        <v>450270</v>
       </c>
       <c r="R11" t="n">
-        <v>7088764</v>
+        <v>7088751</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,6 +1709,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117894225</v>
+        <v>117894228</v>
       </c>
       <c r="B12" t="n">
-        <v>57287</v>
+        <v>90519</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449970</v>
+        <v>450144</v>
       </c>
       <c r="R12" t="n">
-        <v>7089256</v>
+        <v>7088852</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,11 +1816,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117894201</v>
+        <v>117894197</v>
       </c>
       <c r="B13" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450252</v>
+        <v>450230</v>
       </c>
       <c r="R13" t="n">
-        <v>7088672</v>
+        <v>7088707</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117894224</v>
+        <v>117894172</v>
       </c>
       <c r="B14" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>450022</v>
+        <v>449956</v>
       </c>
       <c r="R14" t="n">
-        <v>7089009</v>
+        <v>7089019</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2056,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117894229</v>
+        <v>117894179</v>
       </c>
       <c r="B15" t="n">
-        <v>90517</v>
+        <v>57288</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>450175</v>
+        <v>450114</v>
       </c>
       <c r="R15" t="n">
-        <v>7088816</v>
+        <v>7088861</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,6 +2132,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117894227</v>
+        <v>117894198</v>
       </c>
       <c r="B16" t="n">
-        <v>90517</v>
+        <v>57288</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2174,21 +2179,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>450123</v>
+        <v>450236</v>
       </c>
       <c r="R16" t="n">
-        <v>7088854</v>
+        <v>7088721</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,6 +2239,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117894191</v>
+        <v>117894193</v>
       </c>
       <c r="B17" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2300,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>450212</v>
+        <v>450165</v>
       </c>
       <c r="R17" t="n">
-        <v>7088718</v>
+        <v>7088687</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117894228</v>
+        <v>117894176</v>
       </c>
       <c r="B18" t="n">
-        <v>90517</v>
+        <v>57288</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,21 +2393,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>450144</v>
+        <v>450138</v>
       </c>
       <c r="R18" t="n">
-        <v>7088852</v>
+        <v>7088892</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,6 +2453,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2469,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117894177</v>
+        <v>117894191</v>
       </c>
       <c r="B19" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2509,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>450121</v>
+        <v>450212</v>
       </c>
       <c r="R19" t="n">
-        <v>7088894</v>
+        <v>7088718</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2576,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117894197</v>
+        <v>117894234</v>
       </c>
       <c r="B20" t="n">
-        <v>57287</v>
+        <v>90519</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2592,21 +2607,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2616,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>450230</v>
+        <v>450212</v>
       </c>
       <c r="R20" t="n">
-        <v>7088707</v>
+        <v>7088722</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2652,11 +2667,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2683,10 +2693,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117894173</v>
+        <v>117894219</v>
       </c>
       <c r="B21" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2723,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>449951</v>
+        <v>450218</v>
       </c>
       <c r="R21" t="n">
-        <v>7089007</v>
+        <v>7088983</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,7 +2773,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2790,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117894172</v>
+        <v>117894171</v>
       </c>
       <c r="B22" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2830,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>449956</v>
+        <v>449982</v>
       </c>
       <c r="R22" t="n">
-        <v>7089019</v>
+        <v>7089048</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2870,7 +2880,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2897,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117894218</v>
+        <v>117894199</v>
       </c>
       <c r="B23" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2937,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>450300</v>
+        <v>450248</v>
       </c>
       <c r="R23" t="n">
-        <v>7088949</v>
+        <v>7088702</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,7 +2987,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3004,10 +3014,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117894181</v>
+        <v>117894233</v>
       </c>
       <c r="B24" t="n">
-        <v>57287</v>
+        <v>90519</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3020,21 +3030,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3044,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>450159</v>
+        <v>450244</v>
       </c>
       <c r="R24" t="n">
-        <v>7088815</v>
+        <v>7088764</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3080,11 +3090,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3111,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117894193</v>
+        <v>117894195</v>
       </c>
       <c r="B25" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3151,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>450165</v>
+        <v>450161</v>
       </c>
       <c r="R25" t="n">
-        <v>7088687</v>
+        <v>7088668</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3191,7 +3196,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3218,10 +3223,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117894226</v>
+        <v>117894163</v>
       </c>
       <c r="B26" t="n">
-        <v>90517</v>
+        <v>90501</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3234,21 +3239,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3258,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>449958</v>
+        <v>450323</v>
       </c>
       <c r="R26" t="n">
-        <v>7088997</v>
+        <v>7088910</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3320,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117894219</v>
+        <v>117894220</v>
       </c>
       <c r="B27" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3360,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>450218</v>
+        <v>450212</v>
       </c>
       <c r="R27" t="n">
-        <v>7088983</v>
+        <v>7088954</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3400,7 +3405,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,10 +3432,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117894179</v>
+        <v>117894173</v>
       </c>
       <c r="B28" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3467,10 +3472,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>450114</v>
+        <v>449951</v>
       </c>
       <c r="R28" t="n">
-        <v>7088861</v>
+        <v>7089007</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3534,10 +3539,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117894185</v>
+        <v>117894178</v>
       </c>
       <c r="B29" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3574,10 +3579,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>450127</v>
+        <v>450115</v>
       </c>
       <c r="R29" t="n">
-        <v>7088766</v>
+        <v>7088874</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3614,7 +3619,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3641,10 +3646,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117894199</v>
+        <v>117894224</v>
       </c>
       <c r="B30" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3681,10 +3686,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>450248</v>
+        <v>450022</v>
       </c>
       <c r="R30" t="n">
-        <v>7088702</v>
+        <v>7089009</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3748,10 +3753,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117894238</v>
+        <v>117894225</v>
       </c>
       <c r="B31" t="n">
-        <v>90517</v>
+        <v>57288</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3764,21 +3769,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3788,10 +3793,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>449964</v>
+        <v>449970</v>
       </c>
       <c r="R31" t="n">
-        <v>7089143</v>
+        <v>7089256</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3824,6 +3829,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3850,10 +3860,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117894200</v>
+        <v>117894221</v>
       </c>
       <c r="B32" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3890,10 +3900,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>450233</v>
+        <v>450095</v>
       </c>
       <c r="R32" t="n">
-        <v>7088707</v>
+        <v>7088995</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3957,10 +3967,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117894222</v>
+        <v>117894180</v>
       </c>
       <c r="B33" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3997,10 +4007,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>450034</v>
+        <v>450149</v>
       </c>
       <c r="R33" t="n">
-        <v>7088998</v>
+        <v>7088855</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4064,10 +4074,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117894178</v>
+        <v>117894200</v>
       </c>
       <c r="B34" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4104,10 +4114,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>450115</v>
+        <v>450233</v>
       </c>
       <c r="R34" t="n">
-        <v>7088874</v>
+        <v>7088707</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4144,7 +4154,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4171,10 +4181,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117894180</v>
+        <v>117894227</v>
       </c>
       <c r="B35" t="n">
-        <v>57287</v>
+        <v>90519</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4187,21 +4197,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4211,10 +4221,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>450149</v>
+        <v>450123</v>
       </c>
       <c r="R35" t="n">
-        <v>7088855</v>
+        <v>7088854</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4247,11 +4257,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4278,10 +4283,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117894162</v>
+        <v>117894194</v>
       </c>
       <c r="B36" t="n">
-        <v>90499</v>
+        <v>57288</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4294,21 +4299,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4318,10 +4323,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>450228</v>
+        <v>450163</v>
       </c>
       <c r="R36" t="n">
-        <v>7088763</v>
+        <v>7088675</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4354,6 +4359,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4380,10 +4390,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117894183</v>
+        <v>117894196</v>
       </c>
       <c r="B37" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4420,10 +4430,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>450106</v>
+        <v>450201</v>
       </c>
       <c r="R37" t="n">
-        <v>7088745</v>
+        <v>7088663</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4487,10 +4497,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117894186</v>
+        <v>117894201</v>
       </c>
       <c r="B38" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4527,10 +4537,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>450114</v>
+        <v>450252</v>
       </c>
       <c r="R38" t="n">
-        <v>7088711</v>
+        <v>7088672</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4567,7 +4577,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4594,10 +4604,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117894175</v>
+        <v>117894187</v>
       </c>
       <c r="B39" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4634,10 +4644,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>450026</v>
+        <v>450140</v>
       </c>
       <c r="R39" t="n">
-        <v>7088869</v>
+        <v>7088706</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4674,7 +4684,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4701,10 +4711,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117894230</v>
+        <v>117894222</v>
       </c>
       <c r="B40" t="n">
-        <v>90517</v>
+        <v>57288</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4717,21 +4727,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4741,10 +4751,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>450114</v>
+        <v>450034</v>
       </c>
       <c r="R40" t="n">
-        <v>7088756</v>
+        <v>7088998</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4777,6 +4787,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4803,10 +4818,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117894234</v>
+        <v>117894183</v>
       </c>
       <c r="B41" t="n">
-        <v>90517</v>
+        <v>57288</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4819,21 +4834,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4843,10 +4858,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>450212</v>
+        <v>450106</v>
       </c>
       <c r="R41" t="n">
-        <v>7088722</v>
+        <v>7088745</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4879,6 +4894,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4905,10 +4925,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117894176</v>
+        <v>117894181</v>
       </c>
       <c r="B42" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4945,10 +4965,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>450138</v>
+        <v>450159</v>
       </c>
       <c r="R42" t="n">
-        <v>7088892</v>
+        <v>7088815</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4985,7 +5005,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5012,10 +5032,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117894195</v>
+        <v>117894229</v>
       </c>
       <c r="B43" t="n">
-        <v>57287</v>
+        <v>90519</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5028,21 +5048,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5052,10 +5072,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>450161</v>
+        <v>450175</v>
       </c>
       <c r="R43" t="n">
-        <v>7088668</v>
+        <v>7088816</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5088,11 +5108,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5119,10 +5134,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117894220</v>
+        <v>117894232</v>
       </c>
       <c r="B44" t="n">
-        <v>57287</v>
+        <v>90519</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5135,21 +5150,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5159,10 +5174,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>450212</v>
+        <v>450219</v>
       </c>
       <c r="R44" t="n">
-        <v>7088954</v>
+        <v>7088785</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5195,11 +5210,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5226,10 +5236,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117894192</v>
+        <v>117894230</v>
       </c>
       <c r="B45" t="n">
-        <v>57287</v>
+        <v>90519</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5242,21 +5252,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5266,10 +5276,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>450205</v>
+        <v>450114</v>
       </c>
       <c r="R45" t="n">
-        <v>7088736</v>
+        <v>7088756</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5302,11 +5312,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5333,10 +5338,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117894198</v>
+        <v>117894192</v>
       </c>
       <c r="B46" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5373,10 +5378,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>450236</v>
+        <v>450205</v>
       </c>
       <c r="R46" t="n">
-        <v>7088721</v>
+        <v>7088736</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5413,7 +5418,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5440,10 +5445,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117894190</v>
+        <v>117894174</v>
       </c>
       <c r="B47" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5480,10 +5485,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>450270</v>
+        <v>449965</v>
       </c>
       <c r="R47" t="n">
-        <v>7088751</v>
+        <v>7088991</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5520,7 +5525,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5547,10 +5552,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117894194</v>
+        <v>117894186</v>
       </c>
       <c r="B48" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5587,10 +5592,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>450163</v>
+        <v>450114</v>
       </c>
       <c r="R48" t="n">
-        <v>7088675</v>
+        <v>7088711</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5627,7 +5632,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5654,10 +5659,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117894187</v>
+        <v>117894188</v>
       </c>
       <c r="B49" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5694,10 +5699,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>450140</v>
+        <v>450177</v>
       </c>
       <c r="R49" t="n">
-        <v>7088706</v>
+        <v>7088765</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5734,7 +5739,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5761,10 +5766,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117894171</v>
+        <v>117894162</v>
       </c>
       <c r="B50" t="n">
-        <v>57287</v>
+        <v>90501</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5777,21 +5782,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5801,10 +5806,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>449982</v>
+        <v>450228</v>
       </c>
       <c r="R50" t="n">
-        <v>7089048</v>
+        <v>7088763</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5837,11 +5842,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5868,10 +5868,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117894188</v>
+        <v>117894226</v>
       </c>
       <c r="B51" t="n">
-        <v>57287</v>
+        <v>90519</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5884,21 +5884,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>450177</v>
+        <v>449958</v>
       </c>
       <c r="R51" t="n">
-        <v>7088765</v>
+        <v>7088997</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5944,11 +5944,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5975,10 +5970,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117894232</v>
+        <v>117894177</v>
       </c>
       <c r="B52" t="n">
-        <v>90517</v>
+        <v>57288</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5991,21 +5986,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6015,10 +6010,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>450219</v>
+        <v>450121</v>
       </c>
       <c r="R52" t="n">
-        <v>7088785</v>
+        <v>7088894</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6051,6 +6046,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6077,10 +6077,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117894221</v>
+        <v>117894185</v>
       </c>
       <c r="B53" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6117,10 +6117,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>450095</v>
+        <v>450127</v>
       </c>
       <c r="R53" t="n">
-        <v>7088995</v>
+        <v>7088766</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6184,10 +6184,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117894196</v>
+        <v>117894182</v>
       </c>
       <c r="B54" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6224,10 +6224,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>450201</v>
+        <v>450065</v>
       </c>
       <c r="R54" t="n">
-        <v>7088663</v>
+        <v>7088758</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6291,10 +6291,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117894210</v>
+        <v>117894216</v>
       </c>
       <c r="B55" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6331,10 +6331,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>450351</v>
+        <v>450452</v>
       </c>
       <c r="R55" t="n">
-        <v>7088483</v>
+        <v>7088521</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6398,10 +6398,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117894203</v>
+        <v>117894211</v>
       </c>
       <c r="B56" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6438,10 +6438,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>450380</v>
+        <v>450374</v>
       </c>
       <c r="R56" t="n">
-        <v>7088569</v>
+        <v>7088484</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6478,7 +6478,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6505,10 +6505,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117894204</v>
+        <v>117894203</v>
       </c>
       <c r="B57" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6545,10 +6545,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>450385</v>
+        <v>450380</v>
       </c>
       <c r="R57" t="n">
-        <v>7088570</v>
+        <v>7088569</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6612,10 +6612,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117894205</v>
+        <v>117894237</v>
       </c>
       <c r="B58" t="n">
-        <v>57287</v>
+        <v>90519</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6628,21 +6628,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6652,10 +6652,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>450390</v>
+        <v>450435</v>
       </c>
       <c r="R58" t="n">
-        <v>7088591</v>
+        <v>7088519</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6688,11 +6688,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6719,10 +6714,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117894237</v>
+        <v>117894208</v>
       </c>
       <c r="B59" t="n">
-        <v>90517</v>
+        <v>57288</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6735,21 +6730,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6759,10 +6754,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>450435</v>
+        <v>450348</v>
       </c>
       <c r="R59" t="n">
-        <v>7088519</v>
+        <v>7088372</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6795,6 +6790,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6821,10 +6821,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117894206</v>
+        <v>117894204</v>
       </c>
       <c r="B60" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6861,10 +6861,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>450397</v>
+        <v>450385</v>
       </c>
       <c r="R60" t="n">
-        <v>7088603</v>
+        <v>7088570</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6928,10 +6928,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117894208</v>
+        <v>117894209</v>
       </c>
       <c r="B61" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6968,10 +6968,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>450348</v>
+        <v>450295</v>
       </c>
       <c r="R61" t="n">
-        <v>7088372</v>
+        <v>7088392</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7008,7 +7008,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7035,10 +7035,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117894214</v>
+        <v>117894206</v>
       </c>
       <c r="B62" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7075,10 +7075,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>450390</v>
+        <v>450397</v>
       </c>
       <c r="R62" t="n">
-        <v>7088489</v>
+        <v>7088603</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7142,10 +7142,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117894209</v>
+        <v>117894214</v>
       </c>
       <c r="B63" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7182,10 +7182,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>450295</v>
+        <v>450390</v>
       </c>
       <c r="R63" t="n">
-        <v>7088392</v>
+        <v>7088489</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7249,10 +7249,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117894213</v>
+        <v>117894236</v>
       </c>
       <c r="B64" t="n">
-        <v>57287</v>
+        <v>90519</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7265,21 +7265,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7289,10 +7289,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>450378</v>
+        <v>450337</v>
       </c>
       <c r="R64" t="n">
-        <v>7088494</v>
+        <v>7088500</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7325,11 +7325,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7356,10 +7351,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117894236</v>
+        <v>117894205</v>
       </c>
       <c r="B65" t="n">
-        <v>90517</v>
+        <v>57288</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7372,21 +7367,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7396,10 +7391,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>450337</v>
+        <v>450390</v>
       </c>
       <c r="R65" t="n">
-        <v>7088500</v>
+        <v>7088591</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7432,6 +7427,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7458,10 +7458,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117894235</v>
+        <v>117894213</v>
       </c>
       <c r="B66" t="n">
-        <v>90517</v>
+        <v>57288</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7474,21 +7474,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7498,10 +7498,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>450329</v>
+        <v>450378</v>
       </c>
       <c r="R66" t="n">
-        <v>7088601</v>
+        <v>7088494</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7534,6 +7534,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7560,10 +7565,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117894211</v>
+        <v>117894235</v>
       </c>
       <c r="B67" t="n">
-        <v>57287</v>
+        <v>90519</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7576,21 +7581,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7600,10 +7605,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>450374</v>
+        <v>450329</v>
       </c>
       <c r="R67" t="n">
-        <v>7088484</v>
+        <v>7088601</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7636,11 +7641,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7667,10 +7667,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117894207</v>
+        <v>117894212</v>
       </c>
       <c r="B68" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>450284</v>
+        <v>450373</v>
       </c>
       <c r="R68" t="n">
-        <v>7088356</v>
+        <v>7088492</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7774,10 +7774,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117894216</v>
+        <v>117894207</v>
       </c>
       <c r="B69" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7814,10 +7814,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>450452</v>
+        <v>450284</v>
       </c>
       <c r="R69" t="n">
-        <v>7088521</v>
+        <v>7088356</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7881,10 +7881,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117894212</v>
+        <v>117894210</v>
       </c>
       <c r="B70" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>450373</v>
+        <v>450351</v>
       </c>
       <c r="R70" t="n">
-        <v>7088492</v>
+        <v>7088483</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 57727-2023 artfynd.xlsx
+++ b/artfynd/A 57727-2023 artfynd.xlsx
@@ -2591,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117894234</v>
+        <v>117894219</v>
       </c>
       <c r="B20" t="n">
-        <v>90519</v>
+        <v>57288</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2607,21 +2607,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>450212</v>
+        <v>450218</v>
       </c>
       <c r="R20" t="n">
-        <v>7088722</v>
+        <v>7088983</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2667,6 +2667,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2693,7 +2698,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117894219</v>
+        <v>117894171</v>
       </c>
       <c r="B21" t="n">
         <v>57288</v>
@@ -2733,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>450218</v>
+        <v>449982</v>
       </c>
       <c r="R21" t="n">
-        <v>7088983</v>
+        <v>7089048</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2773,7 +2778,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,7 +2805,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117894171</v>
+        <v>117894199</v>
       </c>
       <c r="B22" t="n">
         <v>57288</v>
@@ -2840,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>449982</v>
+        <v>450248</v>
       </c>
       <c r="R22" t="n">
-        <v>7089048</v>
+        <v>7088702</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2880,7 +2885,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,10 +2912,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117894199</v>
+        <v>117894234</v>
       </c>
       <c r="B23" t="n">
-        <v>57288</v>
+        <v>90519</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2923,21 +2928,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2947,10 +2952,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>450248</v>
+        <v>450212</v>
       </c>
       <c r="R23" t="n">
-        <v>7088702</v>
+        <v>7088722</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2983,11 +2988,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4074,10 +4074,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117894200</v>
+        <v>117894227</v>
       </c>
       <c r="B34" t="n">
-        <v>57288</v>
+        <v>90519</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4090,21 +4090,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>450233</v>
+        <v>450123</v>
       </c>
       <c r="R34" t="n">
-        <v>7088707</v>
+        <v>7088854</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4150,11 +4150,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4181,10 +4176,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117894227</v>
+        <v>117894200</v>
       </c>
       <c r="B35" t="n">
-        <v>90519</v>
+        <v>57288</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4197,21 +4192,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4221,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>450123</v>
+        <v>450233</v>
       </c>
       <c r="R35" t="n">
-        <v>7088854</v>
+        <v>7088707</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4257,6 +4252,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5659,10 +5659,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117894188</v>
+        <v>117894162</v>
       </c>
       <c r="B49" t="n">
-        <v>57288</v>
+        <v>90501</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5675,21 +5675,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>450177</v>
+        <v>450228</v>
       </c>
       <c r="R49" t="n">
-        <v>7088765</v>
+        <v>7088763</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5735,11 +5735,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5766,10 +5761,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117894162</v>
+        <v>117894188</v>
       </c>
       <c r="B50" t="n">
-        <v>90501</v>
+        <v>57288</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5782,21 +5777,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5806,10 +5801,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>450228</v>
+        <v>450177</v>
       </c>
       <c r="R50" t="n">
-        <v>7088763</v>
+        <v>7088765</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5842,6 +5837,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7458,10 +7458,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117894213</v>
+        <v>117894235</v>
       </c>
       <c r="B66" t="n">
-        <v>57288</v>
+        <v>90519</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7474,21 +7474,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7498,10 +7498,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>450378</v>
+        <v>450329</v>
       </c>
       <c r="R66" t="n">
-        <v>7088494</v>
+        <v>7088601</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7534,11 +7534,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7565,10 +7560,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117894235</v>
+        <v>117894213</v>
       </c>
       <c r="B67" t="n">
-        <v>90519</v>
+        <v>57288</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7581,21 +7576,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7605,10 +7600,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>450329</v>
+        <v>450378</v>
       </c>
       <c r="R67" t="n">
-        <v>7088601</v>
+        <v>7088494</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7641,6 +7636,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
